--- a/data/tiktok/data/2026-October-GSM-TT.xlsx
+++ b/data/tiktok/data/2026-October-GSM-TT.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F0C550-17D2-4448-949A-7202FE2E531B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9045185-793C-402A-9EB6-A1C5EEDC3F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14,43 +14,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>ผู้สร้าง</author>
-  </authors>
-  <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">     </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">     </t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>Ad name</t>
   </si>
@@ -73,49 +38,91 @@
     <t/>
   </si>
   <si>
-    <t>Campaign name</t>
-  </si>
-  <si>
-    <t>2105 - Main Account - Video view</t>
+    <t>Ad group ID</t>
+  </si>
+  <si>
+    <t>1877830112516482</t>
+  </si>
+  <si>
+    <t>Ad group name</t>
+  </si>
+  <si>
+    <t>Main Account - Video view</t>
+  </si>
+  <si>
+    <t>Ad ID</t>
+  </si>
+  <si>
+    <t>1877830112516498</t>
   </si>
   <si>
     <t>Spend</t>
   </si>
   <si>
-    <t>2184.63</t>
-  </si>
-  <si>
-    <t>Reach</t>
+    <t>4677.82</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>CPC (destination)</t>
+  </si>
+  <si>
+    <t>CPM</t>
+  </si>
+  <si>
+    <t>11.17</t>
   </si>
   <si>
     <t>Impressions</t>
   </si>
   <si>
-    <t>Video views</t>
-  </si>
-  <si>
-    <t>2-second video views</t>
-  </si>
-  <si>
-    <t>6-second video views</t>
-  </si>
-  <si>
-    <t>Paid likes</t>
-  </si>
-  <si>
-    <t>Paid comments</t>
-  </si>
-  <si>
-    <t>Paid shares</t>
-  </si>
-  <si>
-    <t>Paid follows</t>
-  </si>
-  <si>
-    <t>Paid profile visits</t>
-  </si>
-  <si>
-    <t>Paid favorites</t>
+    <t>Clicks (destination)</t>
+  </si>
+  <si>
+    <t>CTR (destination)</t>
+  </si>
+  <si>
+    <t>Conversions</t>
+  </si>
+  <si>
+    <t>Conversions [SAN]</t>
+  </si>
+  <si>
+    <t>Cost per conversion</t>
+  </si>
+  <si>
+    <t>Cost per conversion [SAN]</t>
+  </si>
+  <si>
+    <t>Conversion rate (CVR, clicks) [SAN]</t>
+  </si>
+  <si>
+    <t>Conversion rate (CVR)</t>
+  </si>
+  <si>
+    <t>Conversion rate (CVR) [SAN]</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>Cost per result</t>
+  </si>
+  <si>
+    <t>28.41</t>
+  </si>
+  <si>
+    <t>Result rate</t>
+  </si>
+  <si>
+    <t>Qualified conversion</t>
+  </si>
+  <si>
+    <t>Cost per qualified conversion</t>
+  </si>
+  <si>
+    <t>Qualified conversion rate</t>
   </si>
   <si>
     <t>Secondary source</t>
@@ -143,7 +150,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,10 +167,6 @@
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -199,10 +202,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -477,11 +481,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -501,49 +505,76 @@
         <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -559,54 +590,80 @@
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2">
-        <v>118304</v>
-      </c>
-      <c r="G2" s="2">
-        <v>223385</v>
-      </c>
-      <c r="H2" s="2">
-        <v>219052</v>
-      </c>
-      <c r="I2" s="2">
-        <v>16302</v>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="J2" s="2">
-        <v>2911</v>
+        <v>418669</v>
       </c>
       <c r="K2" s="2">
-        <v>121</v>
-      </c>
-      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
         <v>0</v>
       </c>
       <c r="M2" s="2">
         <v>0</v>
       </c>
       <c r="N2" s="2">
-        <v>10</v>
-      </c>
-      <c r="O2" s="2">
-        <v>229</v>
-      </c>
-      <c r="P2" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+      <c r="R2" s="3">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2">
+        <v>164653</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0.39329999999999998</v>
+      </c>
+      <c r="W2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>28</v>
+      <c r="X2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>